--- a/data/세부2.xlsx
+++ b/data/세부2.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +38,24 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00B00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,8 +67,13 @@
         <fgColor rgb="0016335E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +95,25 @@
         <color rgb="00D0D7E2"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E6EAF0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E6EAF0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E6EAF0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E6EAF0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +130,19 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,4 +665,200 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>⚠ 자동 생성 탭 — 직접 편집하지 마세요. 일정은 '업무리스트' 탭에서 수정 후 python sync_excel.py 실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>업무명</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>'26 1월</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>'27 1월</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>(예시) 업무 구분 1</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>(예시) 세부2 핵심 연구·실험 항목</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-05~2026-06-30</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="12" t="n"/>
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="12" t="n"/>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr"/>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>(예시) 세부2 중간 점검·보고</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01~2026-09-30</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="12" t="n"/>
+      <c r="N4" s="12" t="n"/>
+      <c r="O4" s="12" t="n"/>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/세부2.xlsx
+++ b/data/세부2.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성능목표실적" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -230,14 +232,39 @@
         <t>같은 키끼리 한 카테고리로 묶임. 막대 색은 키 등장 순서대로 자동(파랑·보라·초록·주황).</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>계획 시작/종료 — 간트 위쪽(계획) 바.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>실적 시작/종료 — 간트 아래쪽(실적) 바. 비우면 실적 바 없음.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>계획서 또는 행정 (비우면 배지 없음).</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>총괄/운영위/DLR/전담 중 쉼표로 구분. 세부과제는 보통 비움.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>sync_excel</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>예: 85% (수동 입력).</t>
       </text>
     </comment>
   </commentList>
@@ -533,17 +560,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,25 +593,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>시작일</t>
+          <t>계획시작</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>종료일</t>
+          <t>계획종료</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>실적시작</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>실적종료</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>주관</t>
         </is>
@@ -610,17 +649,23 @@
       <c r="E2" s="5" t="n">
         <v>46203</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>예시 — 실제 업무로 교체</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>예시 — 실제 업무로 교체 (실적바 예시)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -644,21 +689,23 @@
       <c r="E3" s="5" t="n">
         <v>46295</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"계획서,행정"</formula1>
     </dataValidation>
   </dataValidations>
@@ -668,6 +715,242 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>평가항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>목표</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실적</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>달성도</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>(예시) 평가항목 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>(목표값)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(실적값)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>예시 — 실제 내용으로 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>(예시) 평가항목 2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>성과구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>목표</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실적</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SCI(E) 논문</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>편</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>특허 출원(국내·국제)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>건</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>학술회의 발표</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>건</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -699,7 +982,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>⚠ 자동 생성 탭 — 직접 편집하지 마세요. 일정은 '업무리스트' 탭에서 수정 후 python sync_excel.py 실행.</t>
+          <t>⚠ 자동 생성 탭(계획 기준 미리보기) — 직접 편집 금지. 일정은 '업무리스트'에서 수정 후 python sync_excel.py.</t>
         </is>
       </c>
     </row>
@@ -716,7 +999,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>기간</t>
+          <t>계획기간</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">

--- a/data/세부2.xlsx
+++ b/data/세부2.xlsx
@@ -57,7 +57,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A4FD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,8 +148,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -560,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -635,36 +641,24 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>(예시) 업무 구분 1</t>
+          <t>시험·평가</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>(예시) 세부2 핵심 연구·실험 항목</t>
+          <t>암모니아/바이오연료 연소기 정적 연소성능 시험 및 1차 개선안 도출</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>46027</v>
+        <v>46113</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>46203</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>46034</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>46162</v>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>예시 — 실제 업무로 교체 (실적바 예시)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
+        <v>46356</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
@@ -675,33 +669,81 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>(예시) 업무 구분 1</t>
+          <t>시험·평가</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>(예시) 세부2 중간 점검·보고</t>
+          <t>암모니아 연소 NOx 발생 특성 연구</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>해석·계측</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>상압 조건 암모니아 단일연료 전소 화염 수치해석 및 NOx 예측</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>해석·계측</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>암모니아 직접 분사 연소 및 레이저 계측 화염 특성 진단</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>46387</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -720,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -766,52 +808,96 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>(예시) 평가항목 1</t>
+          <t>NOx 배출</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>(목표값)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>(실적값)</t>
-        </is>
-      </c>
+          <t>최종목표 &lt;100</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>예시 — 실제 내용으로 교체</t>
+          <t>평가시작 1차년도, 해당연도 목표 미명시 / KIMM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>(예시) 평가항목 2</t>
+          <t>레이저응용 물리량 계측수</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>개</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>최종목표 6</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>평가시작 1차년도, 해당연도 목표 미명시 / DLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>NOx 예측 정확도</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>최종목표 90</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1차년도 정확도 70, 2차년도 90% 단계 상향 / KAIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>부분부하 운전한계(Turn-down ratio)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>최종목표 40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>해당연도 목표 미명시 / KIMM</t>
         </is>
       </c>
     </row>
@@ -827,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -867,34 +953,34 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SCI(E) 논문</t>
+          <t>SCI급 게재논문</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>편</t>
+          <t>건</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>1차년도 게재 1편(Proc. Combustion Institute)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>특허 출원(국내·국제)</t>
+          <t>해외참여기관 인력교류(1개월 이상)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -904,7 +990,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -914,34 +1000,84 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>1차년도 누적 0 / 표 주석 표기(3*)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>학술회의 발표</t>
+          <t>세부과제 기술교류회</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>1차년도 실적 1회</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>고용창출 효과</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>1차년도 누적 1명</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>학술발표</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>건</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>예시</t>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2차년도 목표 미명시 / 1차년도 발표 1건</t>
         </is>
       </c>
     </row>
@@ -956,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1081,62 +1217,122 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>(예시) 업무 구분 1</t>
+          <t>시험·평가</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>(예시) 세부2 핵심 연구·실험 항목</t>
+          <t>암모니아/바이오연료 연소기 정적 연소성능 시험 및 1차 개선안 도출</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05~2026-06-30</t>
+          <t>2026-04-01~2026-11-30</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
       <c r="E3" s="11" t="n"/>
       <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
       <c r="J3" s="12" t="n"/>
       <c r="K3" s="12" t="n"/>
       <c r="L3" s="12" t="n"/>
       <c r="M3" s="12" t="n"/>
       <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-      <c r="Q3" s="12" t="n"/>
-      <c r="R3" s="12" t="n"/>
+      <c r="O3" s="11" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr"/>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>(예시) 세부2 중간 점검·보고</t>
+          <t>암모니아 연소 NOx 발생 특성 연구</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01~2026-09-30</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
+          <t>2026-05-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="12" t="n"/>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="11" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
       <c r="M4" s="12" t="n"/>
       <c r="N4" s="12" t="n"/>
       <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="12" t="n"/>
+      <c r="P4" s="11" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>해석·계측</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>상압 조건 암모니아 단일연료 전소 화염 수치해석 및 NOx 예측</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-01~2026-09-30</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n"/>
+      <c r="P5" s="11" t="n"/>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>암모니아 직접 분사 연소 및 레이저 계측 화염 특성 진단</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="13" t="n"/>
+      <c r="P6" s="11" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/세부2.xlsx
+++ b/data/세부2.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성능목표실적" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요일정" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -271,6 +272,21 @@
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>예: 85% (수동 입력).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>sync_excel</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD. 간트차트 위에 ★ 마커로 표시됨.</t>
       </text>
     </comment>
   </commentList>
@@ -1092,6 +1108,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>일정명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/세부2.xlsx
+++ b/data/세부2.xlsx
@@ -671,8 +671,12 @@
       <c r="E2" s="5" t="n">
         <v>46356</v>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="F2" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>46356</v>
+      </c>
       <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
@@ -699,8 +703,12 @@
       <c r="E3" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="F3" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -727,8 +735,12 @@
       <c r="E4" s="5" t="n">
         <v>46295</v>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>46295</v>
+      </c>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
@@ -755,8 +767,12 @@
       <c r="E5" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="F5" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
